--- a/Shop/MSS_Garage_Studio_Budget.xlsx
+++ b/Shop/MSS_Garage_Studio_Budget.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0b129d21d1734229/Documents/Claude/Shop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="490" documentId="11_09570CFE29ECDA9C4BE81FEF5C98E098F6CEC8AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BA3FC4BD-B465-43C4-8219-49ACA8E75421}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="11_09570CFE29ECDA9C4BE81FEF5C98E098F6CEC8AF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8D394B6-8EBC-4E3A-8D62-40C9F6BFFCAC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="810" windowWidth="22110" windowHeight="12070" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="list" sheetId="5" r:id="rId1"/>
@@ -18,14 +18,16 @@
     <sheet name="Budget" sheetId="3" r:id="rId3"/>
     <sheet name="Materials &amp; Budget" sheetId="1" state="hidden" r:id="rId4"/>
     <sheet name="Wall Calculations" sheetId="2" r:id="rId5"/>
+    <sheet name="plywood" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Budget!$A$4:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Budget!$A$4:$I$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Materials &amp; Budget'!$A$4:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">plywood!$B$2:$I$7</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <pivotCaches>
-    <pivotCache cacheId="21" r:id="rId6"/>
+    <pivotCache cacheId="10" r:id="rId7"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="117">
   <si>
     <t>🪵  MSS GARAGE STUDIO — Materials &amp; Budget Tracker</t>
   </si>
@@ -361,6 +363,45 @@
   </si>
   <si>
     <t>cost</t>
+  </si>
+  <si>
+    <t>(Multiple Items)</t>
+  </si>
+  <si>
+    <t>l</t>
+  </si>
+  <si>
+    <t>w</t>
+  </si>
+  <si>
+    <t>price</t>
+  </si>
+  <si>
+    <t>sq fy</t>
+  </si>
+  <si>
+    <t>$/sq-ft</t>
+  </si>
+  <si>
+    <t>Sheets</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>Maple</t>
+  </si>
+  <si>
+    <t>Luauan</t>
+  </si>
+  <si>
+    <t>Birch</t>
+  </si>
+  <si>
+    <t>area</t>
+  </si>
+  <si>
+    <t>Plywood 4×8 (Wall Panels)</t>
   </si>
 </sst>
 </file>
@@ -629,11 +670,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -766,13 +808,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="44" fontId="18" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -788,12 +836,6 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -818,13 +860,122 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="17" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="17" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="30">
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -842,17 +993,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Stephen Bozzone" refreshedDate="46083.921246296297" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="14" xr:uid="{AC23A2BC-DFE7-4CF1-897D-FFAC7DE01F78}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Stephen Bozzone" refreshedDate="46089.637815509261" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="13" xr:uid="{AC23A2BC-DFE7-4CF1-897D-FFAC7DE01F78}">
   <cacheSource type="worksheet">
-    <worksheetSource ref="A4:I18" sheet="Budget"/>
+    <worksheetSource ref="A4:I17" sheet="Budget"/>
   </cacheSource>
   <cacheFields count="9">
     <cacheField name="ITEM" numFmtId="0">
-      <sharedItems count="14">
+      <sharedItems count="15">
         <s v="Hardwood Penetrating Oil Finish (quart)"/>
-        <s v="Lauan Plywood 4×8 (Wall Panels)"/>
+        <s v="Plywood 4×8 (Wall Panels)"/>
         <s v="Construction Adhesive (Liquid Nails)"/>
-        <s v="1/8&quot; hardboard"/>
         <s v="Lumber Rack Brackets (Heavy-Duty Steel)"/>
         <s v="Lag Bolts + Wall Anchors Assortment"/>
         <s v="Floating Shelf Brackets (16&quot; Depth)"/>
@@ -863,6 +1013,8 @@
         <s v="Laminate, grey"/>
         <s v="3/4&quot;  Plywood 4×8 (Bench top lamination)"/>
         <s v="Wall Control Metal Pegboard Kit (2-pack)"/>
+        <s v="Lauan Plywood 4×8 (Wall Panels)" u="1"/>
+        <s v="1/8&quot; hardboard" u="1"/>
       </sharedItems>
     </cacheField>
     <cacheField name="Phase" numFmtId="0">
@@ -892,13 +1044,19 @@
       </sharedItems>
     </cacheField>
     <cacheField name="REQUIRED_x000a_QTY" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="15"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
     </cacheField>
     <cacheField name="ON HAND_x000a_QTY" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="9"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="15"/>
     </cacheField>
     <cacheField name="TO PURCHASE" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="9"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="9" count="5">
+        <n v="0"/>
+        <n v="6"/>
+        <n v="2"/>
+        <n v="1"/>
+        <n v="9" u="1"/>
+      </sharedItems>
     </cacheField>
     <cacheField name="UNIT_x000a_COST" numFmtId="164">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="285"/>
@@ -916,28 +1074,28 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="14">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="13">
   <r>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
     <x v="0"/>
-    <n v="1"/>
     <n v="0"/>
-    <n v="1"/>
+    <n v="0"/>
+    <x v="0"/>
     <n v="68.67"/>
-    <n v="68.67"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="1"/>
     <x v="0"/>
     <x v="1"/>
     <x v="1"/>
-    <n v="9"/>
+    <n v="6"/>
     <n v="0"/>
-    <n v="9"/>
-    <n v="14.98"/>
-    <n v="134.82"/>
+    <x v="1"/>
+    <n v="37.479999999999997"/>
+    <n v="224.88"/>
   </r>
   <r>
     <x v="2"/>
@@ -946,128 +1104,117 @@
     <x v="1"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="2"/>
+    <x v="2"/>
     <n v="7.49"/>
     <n v="14.98"/>
   </r>
   <r>
     <x v="3"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <n v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="6"/>
+    <n v="6"/>
+    <x v="0"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="14.28"/>
-    <n v="14.28"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="4"/>
     <x v="1"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="6"/>
-    <n v="6"/>
-    <n v="0"/>
-    <n v="0"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="18.489999999999998"/>
     <n v="0"/>
   </r>
   <r>
     <x v="5"/>
-    <x v="1"/>
+    <x v="2"/>
+    <x v="3"/>
     <x v="0"/>
-    <x v="1"/>
-    <n v="1"/>
+    <n v="2"/>
+    <n v="2"/>
+    <x v="0"/>
+    <n v="37.950000000000003"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="18.489999999999998"/>
-    <n v="18.489999999999998"/>
   </r>
   <r>
     <x v="6"/>
     <x v="2"/>
     <x v="3"/>
     <x v="0"/>
-    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <x v="0"/>
+    <n v="42.49"/>
     <n v="0"/>
-    <n v="2"/>
-    <n v="37.950000000000003"/>
-    <n v="75.900000000000006"/>
   </r>
   <r>
     <x v="7"/>
     <x v="2"/>
     <x v="3"/>
-    <x v="0"/>
+    <x v="1"/>
     <n v="1"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="42.49"/>
-    <n v="42.49"/>
+    <x v="3"/>
+    <n v="64.97"/>
+    <n v="64.97"/>
   </r>
   <r>
     <x v="8"/>
     <x v="2"/>
-    <x v="3"/>
+    <x v="2"/>
     <x v="1"/>
-    <n v="1"/>
+    <n v="15"/>
+    <n v="15"/>
+    <x v="0"/>
+    <n v="8.98"/>
     <n v="0"/>
-    <n v="1"/>
-    <n v="64.97"/>
-    <n v="64.97"/>
   </r>
   <r>
     <x v="9"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="1"/>
-    <n v="15"/>
-    <n v="9"/>
-    <n v="6"/>
-    <n v="8.98"/>
-    <n v="53.88"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="8"/>
+    <n v="8"/>
+    <x v="0"/>
+    <n v="23.25"/>
+    <n v="0"/>
   </r>
   <r>
     <x v="10"/>
     <x v="3"/>
     <x v="4"/>
-    <x v="0"/>
-    <n v="8"/>
-    <n v="8"/>
+    <x v="1"/>
+    <n v="1"/>
     <n v="0"/>
-    <n v="23.25"/>
-    <n v="0"/>
+    <x v="3"/>
+    <n v="61.44"/>
+    <n v="61.44"/>
   </r>
   <r>
     <x v="11"/>
     <x v="3"/>
     <x v="4"/>
     <x v="1"/>
-    <n v="1"/>
-    <n v="0"/>
-    <n v="1"/>
-    <n v="61.44"/>
-    <n v="61.44"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="1"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="2"/>
+    <x v="2"/>
     <n v="64.97"/>
     <n v="129.94"/>
   </r>
   <r>
-    <x v="13"/>
+    <x v="12"/>
     <x v="4"/>
     <x v="2"/>
     <x v="3"/>
     <n v="2"/>
     <n v="0"/>
-    <n v="2"/>
+    <x v="2"/>
     <n v="285"/>
     <n v="570"/>
   </r>
@@ -1075,25 +1222,26 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E77E405-CB24-4475-870C-D5B876DBCC91}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:E17" firstHeaderRow="1" firstDataRow="3" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E77E405-CB24-4475-870C-D5B876DBCC91}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:C11" firstHeaderRow="1" firstDataRow="3" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
-      <items count="15">
+      <items count="16">
+        <item x="5"/>
+        <item x="9"/>
+        <item x="0"/>
         <item x="6"/>
-        <item h="1" x="10"/>
-        <item x="0"/>
+        <item m="1" x="14"/>
+        <item x="11"/>
         <item x="7"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="10"/>
+        <item m="1" x="13"/>
         <item x="3"/>
         <item x="12"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="5"/>
-        <item x="11"/>
         <item x="1"/>
-        <item x="4"/>
-        <item x="13"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1101,35 +1249,32 @@
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="5">
-        <item x="0"/>
+        <item h="1" x="0"/>
         <item h="1" x="2"/>
         <item x="1"/>
         <item h="1" x="3"/>
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField multipleItemSelectionAllowed="1" showAll="0"/>
     <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="6">
+        <item h="1" x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item m="1" x="4"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField dataField="1" numFmtId="164" showAll="0"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="12">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
+  <rowItems count="6">
     <i>
       <x v="5"/>
     </i>
@@ -1137,19 +1282,13 @@
       <x v="6"/>
     </i>
     <i>
-      <x v="7"/>
-    </i>
-    <i>
       <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
     </i>
     <i>
       <x v="10"/>
     </i>
     <i>
-      <x v="11"/>
+      <x v="14"/>
     </i>
     <i t="grand">
       <x/>
@@ -1159,14 +1298,7 @@
     <field x="3"/>
     <field x="-2"/>
   </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1" i="1">
-      <x v="1"/>
-    </i>
+  <colItems count="2">
     <i>
       <x v="2"/>
       <x/>
@@ -1175,10 +1307,58 @@
       <x v="1"/>
     </i>
   </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
   <dataFields count="2">
     <dataField name="quan" fld="6" baseField="0" baseItem="0"/>
     <dataField name="cost" fld="8" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
+  <formats count="5">
+    <format dxfId="29">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="28">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="6" count="0"/>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="27">
+      <pivotArea field="3" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisCol" fieldPosition="0"/>
+    </format>
+    <format dxfId="26">
+      <pivotArea dataOnly="0" labelOnly="1" fieldPosition="0">
+        <references count="1">
+          <reference field="3" count="1">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+    <format dxfId="25">
+      <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1">
+            <x v="0"/>
+          </reference>
+          <reference field="3" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </format>
+  </formats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -1192,25 +1372,26 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A767B7C-2B5F-4C6B-834C-3852A2317187}" name="PivotTable1" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:D28" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1A767B7C-2B5F-4C6B-834C-3852A2317187}" name="PivotTable1" cacheId="10" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:D26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField axis="axisRow" showAll="0">
-      <items count="15">
+      <items count="16">
+        <item x="11"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="2"/>
+        <item x="5"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item m="1" x="13"/>
+        <item x="6"/>
+        <item x="3"/>
         <item x="12"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="2"/>
-        <item x="6"/>
+        <item m="1" x="14"/>
         <item x="10"/>
-        <item x="0"/>
-        <item x="5"/>
         <item x="1"/>
-        <item x="7"/>
-        <item x="4"/>
-        <item x="13"/>
-        <item x="3"/>
-        <item x="11"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -1254,7 +1435,7 @@
     <field x="2"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="24">
+  <rowItems count="22">
     <i>
       <x/>
     </i>
@@ -1271,7 +1452,7 @@
       <x v="4"/>
     </i>
     <i r="2">
-      <x v="8"/>
+      <x v="14"/>
     </i>
     <i>
       <x v="1"/>
@@ -1281,12 +1462,6 @@
     </i>
     <i r="2">
       <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="2">
-      <x v="12"/>
     </i>
     <i>
       <x v="2"/>
@@ -1642,213 +1817,143 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA1BC734-9EB3-4BFD-8CAD-7C1758009F35}">
-  <dimension ref="A3:E43"/>
+  <dimension ref="A1:C43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.90625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.7265625" style="28" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.81640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B3" s="38" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="28" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" s="72" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" s="28" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C4" s="28"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="28" t="s">
         <v>102</v>
       </c>
       <c r="C5" t="s">
         <v>103</v>
       </c>
-      <c r="D5" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="66">
+        <v>80</v>
+      </c>
+      <c r="B6" s="73">
         <v>2</v>
       </c>
       <c r="C6" s="27">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="D6" s="66"/>
-      <c r="E6" s="27"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+        <v>129.94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" s="39" t="s">
-        <v>28</v>
-      </c>
-      <c r="B7" s="66">
+        <v>93</v>
+      </c>
+      <c r="B7" s="73">
         <v>1</v>
       </c>
       <c r="C7" s="27">
-        <v>68.67</v>
-      </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="27"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+        <v>64.97</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="39" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="66">
+        <v>33</v>
+      </c>
+      <c r="B8" s="73">
+        <v>2</v>
+      </c>
+      <c r="C8" s="27">
+        <v>14.98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" s="73">
         <v>1</v>
       </c>
-      <c r="C8" s="27">
-        <v>42.49</v>
-      </c>
-      <c r="D8" s="66"/>
-      <c r="E8" s="27"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="39" t="s">
-        <v>100</v>
-      </c>
-      <c r="B9" s="66"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="66">
-        <v>1</v>
-      </c>
-      <c r="E9" s="27">
-        <v>14.28</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C9" s="27">
+        <v>61.44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" s="66"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="66">
-        <v>2</v>
-      </c>
-      <c r="E10" s="27">
-        <v>129.94</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="B10" s="73">
+        <v>6</v>
+      </c>
+      <c r="C10" s="27">
+        <v>224.88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="39" t="s">
-        <v>93</v>
-      </c>
-      <c r="B11" s="66"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="66">
-        <v>1</v>
-      </c>
-      <c r="E11" s="27">
-        <v>64.97</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="39" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="66"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="66">
-        <v>6</v>
-      </c>
-      <c r="E12" s="27">
-        <v>53.88</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="39" t="s">
-        <v>33</v>
-      </c>
-      <c r="B13" s="66"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="66">
-        <v>2</v>
-      </c>
-      <c r="E13" s="27">
-        <v>14.98</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="39" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="66"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="66">
-        <v>1</v>
-      </c>
-      <c r="E14" s="27">
-        <v>18.489999999999998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="39" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="66">
-        <v>1</v>
-      </c>
-      <c r="E15" s="27">
-        <v>61.44</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="39" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="66"/>
-      <c r="C16" s="27"/>
-      <c r="D16" s="66">
-        <v>9</v>
-      </c>
-      <c r="E16" s="27">
-        <v>134.82</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="39" t="s">
         <v>96</v>
       </c>
-      <c r="B17" s="66">
-        <v>4</v>
-      </c>
-      <c r="C17" s="27">
-        <v>187.06</v>
-      </c>
-      <c r="D17" s="66">
-        <v>23</v>
-      </c>
-      <c r="E17" s="27">
-        <v>492.8</v>
-      </c>
+      <c r="B11" s="73">
+        <v>12</v>
+      </c>
+      <c r="C11" s="27">
+        <v>496.21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B12"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B13"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B14"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B15"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B16"/>
+    </row>
+    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B17"/>
+    </row>
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B18"/>
+    </row>
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B19"/>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" s="39" t="s">
@@ -1912,7 +2017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{952942DC-7CD0-44C8-8CCD-BFD1B5E43716}">
-  <dimension ref="A3:D28"/>
+  <dimension ref="A3:D26"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="41.81640625" bestFit="1" customWidth="1"/>
@@ -1920,10 +2025,10 @@
     <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.90625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.90625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
@@ -1955,13 +2060,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="27">
-        <v>68.67</v>
+        <v>0</v>
       </c>
       <c r="C5" s="27">
-        <v>149.79999999999998</v>
+        <v>239.85999999999999</v>
       </c>
       <c r="D5" s="27">
-        <v>218.47</v>
+        <v>239.85999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
@@ -1969,13 +2074,13 @@
         <v>91</v>
       </c>
       <c r="B6" s="27">
-        <v>68.67</v>
+        <v>0</v>
       </c>
       <c r="C6" s="27">
         <v>14.98</v>
       </c>
       <c r="D6" s="27">
-        <v>83.65</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
@@ -1995,11 +2100,11 @@
         <v>28</v>
       </c>
       <c r="B8" s="27">
-        <v>68.67</v>
+        <v>0</v>
       </c>
       <c r="C8" s="27"/>
       <c r="D8" s="27">
-        <v>68.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
@@ -2008,22 +2113,22 @@
       </c>
       <c r="B9" s="27"/>
       <c r="C9" s="27">
-        <v>134.82</v>
+        <v>224.88</v>
       </c>
       <c r="D9" s="27">
-        <v>134.82</v>
+        <v>224.88</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="42" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="B10" s="27"/>
       <c r="C10" s="27">
-        <v>134.82</v>
+        <v>224.88</v>
       </c>
       <c r="D10" s="27">
-        <v>134.82</v>
+        <v>224.88</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
@@ -2032,10 +2137,10 @@
       </c>
       <c r="B11" s="27"/>
       <c r="C11" s="27">
-        <v>32.769999999999996</v>
+        <v>0</v>
       </c>
       <c r="D11" s="27">
-        <v>32.769999999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
@@ -2044,10 +2149,10 @@
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27">
-        <v>18.489999999999998</v>
+        <v>0</v>
       </c>
       <c r="D12" s="27">
-        <v>18.489999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
@@ -2056,200 +2161,176 @@
       </c>
       <c r="B13" s="27"/>
       <c r="C13" s="27">
-        <v>18.489999999999998</v>
+        <v>0</v>
       </c>
       <c r="D13" s="27">
-        <v>18.489999999999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="B14" s="27"/>
+      <c r="A14" s="39">
+        <v>3</v>
+      </c>
+      <c r="B14" s="27">
+        <v>0</v>
+      </c>
       <c r="C14" s="27">
-        <v>14.28</v>
+        <v>64.97</v>
       </c>
       <c r="D14" s="27">
-        <v>14.28</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="27"/>
+      <c r="A15" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="B15" s="27">
+        <v>0</v>
+      </c>
       <c r="C15" s="27">
-        <v>14.28</v>
+        <v>64.97</v>
       </c>
       <c r="D15" s="27">
-        <v>14.28</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="39">
-        <v>3</v>
-      </c>
-      <c r="B16" s="27">
-        <v>118.39000000000001</v>
-      </c>
+      <c r="A16" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="27"/>
       <c r="C16" s="27">
-        <v>118.85</v>
+        <v>64.97</v>
       </c>
       <c r="D16" s="27">
-        <v>237.24</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="40" t="s">
-        <v>83</v>
+      <c r="A17" s="42" t="s">
+        <v>17</v>
       </c>
       <c r="B17" s="27">
-        <v>118.39000000000001</v>
-      </c>
-      <c r="C17" s="27">
-        <v>64.97</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="C17" s="27"/>
       <c r="D17" s="27">
-        <v>183.36</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="42" t="s">
-        <v>93</v>
-      </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27">
-        <v>64.97</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B18" s="27">
+        <v>0</v>
+      </c>
+      <c r="C18" s="27"/>
       <c r="D18" s="27">
-        <v>64.97</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="42" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="27">
-        <v>75.900000000000006</v>
-      </c>
-      <c r="C19" s="27"/>
+      <c r="A19" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="27"/>
+      <c r="C19" s="27">
+        <v>0</v>
+      </c>
       <c r="D19" s="27">
-        <v>75.900000000000006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="42" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="27">
-        <v>42.49</v>
-      </c>
-      <c r="C20" s="27"/>
+        <v>20</v>
+      </c>
+      <c r="B20" s="27"/>
+      <c r="C20" s="27">
+        <v>0</v>
+      </c>
       <c r="D20" s="27">
-        <v>42.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="B21" s="27"/>
+      <c r="A21" s="39">
+        <v>4</v>
+      </c>
+      <c r="B21" s="27">
+        <v>0</v>
+      </c>
       <c r="C21" s="27">
-        <v>53.88</v>
+        <v>191.38</v>
       </c>
       <c r="D21" s="27">
-        <v>53.88</v>
+        <v>191.38</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="27"/>
+      <c r="A22" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="B22" s="27">
+        <v>0</v>
+      </c>
       <c r="C22" s="27">
-        <v>53.88</v>
+        <v>191.38</v>
       </c>
       <c r="D22" s="27">
-        <v>53.88</v>
+        <v>191.38</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="39">
-        <v>4</v>
-      </c>
-      <c r="B23" s="27">
-        <v>0</v>
-      </c>
+      <c r="A23" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B23" s="27"/>
       <c r="C23" s="27">
-        <v>191.38</v>
+        <v>129.94</v>
       </c>
       <c r="D23" s="27">
-        <v>191.38</v>
+        <v>129.94</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="40" t="s">
-        <v>82</v>
+      <c r="A24" s="42" t="s">
+        <v>13</v>
       </c>
       <c r="B24" s="27">
         <v>0</v>
       </c>
-      <c r="C24" s="27">
-        <v>191.38</v>
-      </c>
+      <c r="C24" s="27"/>
       <c r="D24" s="27">
-        <v>191.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" s="42" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="B25" s="27"/>
       <c r="C25" s="27">
-        <v>129.94</v>
+        <v>61.44</v>
       </c>
       <c r="D25" s="27">
-        <v>129.94</v>
+        <v>61.44</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="42" t="s">
-        <v>13</v>
+      <c r="A26" s="39" t="s">
+        <v>96</v>
       </c>
       <c r="B26" s="27">
         <v>0</v>
       </c>
-      <c r="C26" s="27"/>
+      <c r="C26" s="27">
+        <v>496.21</v>
+      </c>
       <c r="D26" s="27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27">
-        <v>61.44</v>
-      </c>
-      <c r="D27" s="27">
-        <v>61.44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="39" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" s="27">
-        <v>187.06</v>
-      </c>
-      <c r="C28" s="27">
-        <v>492.8</v>
-      </c>
-      <c r="D28" s="27">
-        <v>679.86000000000013</v>
+        <v>496.21</v>
       </c>
     </row>
   </sheetData>
@@ -2260,53 +2341,53 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44F60687-3931-4551-ABBC-9C01622620C5}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:O32"/>
+  <dimension ref="A1:O31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
     <col min="2" max="2" width="10.36328125" customWidth="1"/>
     <col min="3" max="3" width="11.7265625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.81640625" style="28" customWidth="1"/>
-    <col min="5" max="6" width="9.36328125" style="28" customWidth="1"/>
+    <col min="5" max="6" width="9.453125" style="28" customWidth="1"/>
     <col min="7" max="7" width="11" style="28" customWidth="1"/>
-    <col min="8" max="8" width="9.36328125" style="31" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" style="31" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.26953125" style="31" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.36328125" style="31" customWidth="1"/>
+    <col min="10" max="10" width="9.453125" style="31" customWidth="1"/>
     <col min="11" max="11" width="10.36328125" style="31" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="48" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
-      <c r="K1" s="50"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="50" t="s">
         <v>90</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-    </row>
-    <row r="3" spans="1:15" ht="8" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="50"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+    </row>
+    <row r="3" spans="1:15" ht="8.15" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:15" s="28" customFormat="1" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>2</v>
@@ -2342,7 +2423,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
         <v>28</v>
       </c>
@@ -2356,21 +2437,21 @@
         <v>14</v>
       </c>
       <c r="E5" s="6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="6">
         <v>0</v>
       </c>
       <c r="G5" s="7">
         <f>MAX(E5-F5,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="8">
         <v>68.67</v>
       </c>
       <c r="I5" s="9">
         <f>G5*H5</f>
-        <v>68.67</v>
+        <v>0</v>
       </c>
       <c r="J5" s="41">
         <f>F5*H5</f>
@@ -2378,14 +2459,14 @@
       </c>
       <c r="K5" s="2">
         <f>E5*H5</f>
-        <v>68.67</v>
+        <v>0</v>
       </c>
       <c r="N5" s="27"/>
       <c r="O5" s="27"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="B6" s="6">
         <v>1</v>
@@ -2397,29 +2478,31 @@
         <v>15</v>
       </c>
       <c r="E6" s="6">
-        <v>9</v>
+        <f>plywood!H3</f>
+        <v>6</v>
       </c>
       <c r="F6" s="6">
         <v>0</v>
       </c>
       <c r="G6" s="7">
-        <f t="shared" ref="G6:G18" si="0">MAX(E6-F6,0)</f>
-        <v>9</v>
+        <f t="shared" ref="G6:G17" si="0">MAX(E6-F6,0)</f>
+        <v>6</v>
       </c>
       <c r="H6" s="8">
-        <v>14.98</v>
+        <f>plywood!E3</f>
+        <v>37.479999999999997</v>
       </c>
       <c r="I6" s="9">
-        <f t="shared" ref="I6:I18" si="1">G6*H6</f>
-        <v>134.82</v>
+        <f t="shared" ref="I6:I17" si="1">G6*H6</f>
+        <v>224.88</v>
       </c>
       <c r="J6" s="41">
-        <f t="shared" ref="J6:J18" si="2">F6*H6</f>
+        <f t="shared" ref="J6:J17" si="2">F6*H6</f>
         <v>0</v>
       </c>
       <c r="K6" s="2">
-        <f t="shared" ref="K6:K18" si="3">E6*H6</f>
-        <v>134.82</v>
+        <f t="shared" ref="K6:K17" si="3">E6*H6</f>
+        <v>224.88</v>
       </c>
       <c r="N6" s="27"/>
       <c r="O6" s="27"/>
@@ -2465,35 +2548,35 @@
       <c r="N7" s="27"/>
       <c r="O7" s="27"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="B8" s="6">
         <v>2</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>15</v>
+        <v>86</v>
       </c>
       <c r="E8" s="6">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F8" s="6">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="8">
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="I8" s="9">
         <f t="shared" si="1"/>
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="J8" s="41">
         <f t="shared" si="2"/>
@@ -2501,36 +2584,36 @@
       </c>
       <c r="K8" s="2">
         <f t="shared" si="3"/>
-        <v>14.28</v>
+        <v>0</v>
       </c>
       <c r="N8" s="27"/>
       <c r="O8" s="27"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6">
         <v>2</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="E9" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F9" s="6">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="7">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="H9" s="8">
-        <v>0</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="I9" s="9">
         <f t="shared" si="1"/>
@@ -2538,59 +2621,59 @@
       </c>
       <c r="J9" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="K9" s="2">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>18.489999999999998</v>
       </c>
       <c r="N9" s="27"/>
       <c r="O9" s="27"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B10" s="6">
+        <v>3</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="6">
         <v>2</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="6">
-        <v>1</v>
-      </c>
       <c r="F10" s="6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G10" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" s="8">
-        <v>18.489999999999998</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="I10" s="9">
         <f t="shared" si="1"/>
-        <v>18.489999999999998</v>
+        <v>0</v>
       </c>
       <c r="J10" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="K10" s="2">
         <f t="shared" si="3"/>
-        <v>18.489999999999998</v>
+        <v>75.900000000000006</v>
       </c>
       <c r="N10" s="27"/>
       <c r="O10" s="27"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B11" s="6">
         <v>3</v>
@@ -2602,36 +2685,36 @@
         <v>14</v>
       </c>
       <c r="E11" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F11" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="7">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H11" s="8">
-        <v>37.950000000000003</v>
+        <v>42.49</v>
       </c>
       <c r="I11" s="9">
         <f t="shared" si="1"/>
-        <v>75.900000000000006</v>
+        <v>0</v>
       </c>
       <c r="J11" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>42.49</v>
       </c>
       <c r="K11" s="2">
         <f t="shared" si="3"/>
-        <v>75.900000000000006</v>
+        <v>42.49</v>
       </c>
       <c r="N11" s="27"/>
       <c r="O11" s="27"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>18</v>
+        <v>93</v>
       </c>
       <c r="B12" s="6">
         <v>3</v>
@@ -2640,7 +2723,7 @@
         <v>83</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E12" s="6">
         <v>1</v>
@@ -2653,11 +2736,11 @@
         <v>1</v>
       </c>
       <c r="H12" s="8">
-        <v>42.49</v>
+        <v>64.97</v>
       </c>
       <c r="I12" s="9">
         <f t="shared" si="1"/>
-        <v>42.49</v>
+        <v>64.97</v>
       </c>
       <c r="J12" s="41">
         <f t="shared" si="2"/>
@@ -2665,96 +2748,96 @@
       </c>
       <c r="K12" s="2">
         <f t="shared" si="3"/>
-        <v>42.49</v>
+        <v>64.97</v>
       </c>
       <c r="N12" s="27"/>
       <c r="O12" s="27"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>93</v>
+        <v>20</v>
       </c>
       <c r="B13" s="6">
         <v>3</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>15</v>
       </c>
       <c r="E13" s="6">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="F13" s="6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G13" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H13" s="8">
-        <v>64.97</v>
+        <v>8.98</v>
       </c>
       <c r="I13" s="9">
         <f t="shared" si="1"/>
-        <v>64.97</v>
+        <v>0</v>
       </c>
       <c r="J13" s="41">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>134.70000000000002</v>
       </c>
       <c r="K13" s="2">
         <f t="shared" si="3"/>
-        <v>64.97</v>
+        <v>134.70000000000002</v>
       </c>
       <c r="N13" s="27"/>
       <c r="O13" s="27"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B14" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E14" s="6">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F14" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="7">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H14" s="8">
-        <v>8.98</v>
+        <v>23.25</v>
       </c>
       <c r="I14" s="9">
         <f t="shared" si="1"/>
-        <v>53.88</v>
+        <v>0</v>
       </c>
       <c r="J14" s="41">
         <f t="shared" si="2"/>
-        <v>80.820000000000007</v>
+        <v>186</v>
       </c>
       <c r="K14" s="2">
         <f t="shared" si="3"/>
-        <v>134.70000000000002</v>
+        <v>186</v>
       </c>
       <c r="N14" s="27"/>
       <c r="O14" s="27"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="4" t="s">
-        <v>13</v>
+        <v>101</v>
       </c>
       <c r="B15" s="6">
         <v>4</v>
@@ -2763,39 +2846,39 @@
         <v>82</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E15" s="6">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F15" s="6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G15" s="7">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" s="8">
-        <v>23.25</v>
+        <v>61.44</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>G15*H15</f>
+        <v>61.44</v>
       </c>
       <c r="J15" s="41">
         <f t="shared" si="2"/>
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2">
         <f t="shared" si="3"/>
-        <v>186</v>
+        <v>61.44</v>
       </c>
       <c r="N15" s="27"/>
       <c r="O15" s="27"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="4" t="s">
-        <v>101</v>
+        <v>80</v>
       </c>
       <c r="B16" s="6">
         <v>4</v>
@@ -2807,21 +2890,21 @@
         <v>15</v>
       </c>
       <c r="E16" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="6">
         <v>0</v>
       </c>
       <c r="G16" s="7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" s="8">
-        <v>61.44</v>
+        <v>64.97</v>
       </c>
       <c r="I16" s="9">
-        <f>G16*H16</f>
-        <v>61.44</v>
+        <f t="shared" si="1"/>
+        <v>129.94</v>
       </c>
       <c r="J16" s="41">
         <f t="shared" si="2"/>
@@ -2829,23 +2912,23 @@
       </c>
       <c r="K16" s="2">
         <f t="shared" si="3"/>
-        <v>61.44</v>
+        <v>129.94</v>
       </c>
       <c r="N16" s="27"/>
       <c r="O16" s="27"/>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="B17" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E17" s="6">
         <v>2</v>
@@ -2858,11 +2941,11 @@
         <v>2</v>
       </c>
       <c r="H17" s="8">
-        <v>64.97</v>
+        <v>285</v>
       </c>
       <c r="I17" s="9">
         <f t="shared" si="1"/>
-        <v>129.94</v>
+        <v>570</v>
       </c>
       <c r="J17" s="41">
         <f t="shared" si="2"/>
@@ -2870,211 +2953,170 @@
       </c>
       <c r="K17" s="2">
         <f t="shared" si="3"/>
-        <v>129.94</v>
+        <v>570</v>
       </c>
       <c r="N17" s="27"/>
       <c r="O17" s="27"/>
     </row>
-    <row r="18" spans="1:15" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="6">
-        <v>5</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2</v>
-      </c>
-      <c r="F18" s="6">
-        <v>0</v>
-      </c>
-      <c r="G18" s="7">
-        <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="H18" s="8">
-        <v>285</v>
-      </c>
-      <c r="I18" s="9">
-        <f t="shared" si="1"/>
-        <v>570</v>
-      </c>
-      <c r="J18" s="41">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="2">
-        <f t="shared" si="3"/>
-        <v>570</v>
-      </c>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="4"/>
+      <c r="B18" s="34"/>
+      <c r="C18" s="34"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="37"/>
+      <c r="H18" s="8"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
+      <c r="K18" s="9"/>
       <c r="N18" s="27"/>
       <c r="O18" s="27"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="4"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="35"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="N19" s="27"/>
-      <c r="O19" s="27"/>
-    </row>
-    <row r="20" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="s">
+    <row r="19" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A19" s="32" t="s">
         <v>34</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="33"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="10" t="s">
+      <c r="B19" s="33"/>
+      <c r="C19" s="33"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="I20" s="11">
-        <f>SUBTOTAL(109,I5:I18)</f>
-        <v>679.86000000000013</v>
-      </c>
-      <c r="J20" s="11">
-        <f>SUBTOTAL(109,J5:J18)</f>
-        <v>266.82</v>
-      </c>
-      <c r="K20" s="11">
-        <f>SUBTOTAL(109,K5:K18)</f>
-        <v>946.68000000000006</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="54" t="s">
+      <c r="I19" s="11">
+        <f>SUBTOTAL(109,I5:I17)</f>
+        <v>496.21</v>
+      </c>
+      <c r="J19" s="11">
+        <f>SUBTOTAL(109,J5:J17)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="11">
+        <f>SUBTOTAL(109,K5:K17)</f>
+        <v>496.21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="55"/>
-      <c r="C22" s="55"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="50"/>
-      <c r="I22" s="50"/>
-      <c r="J22" s="50"/>
-      <c r="K22" s="50"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="49"/>
+      <c r="E21" s="49"/>
+      <c r="F21" s="49"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="49"/>
+      <c r="K21" s="49"/>
+    </row>
+    <row r="22" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="53" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="54"/>
+      <c r="C22" s="54"/>
+      <c r="D22" s="54"/>
+      <c r="E22" s="54"/>
+      <c r="F22" s="54"/>
+      <c r="G22" s="54"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="54"/>
+      <c r="J22" s="55"/>
+      <c r="K22" s="12">
+        <f>K19</f>
+        <v>496.21</v>
+      </c>
     </row>
     <row r="23" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A23" s="51" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="52"/>
-      <c r="C23" s="52"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
-      <c r="F23" s="52"/>
-      <c r="G23" s="52"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="52"/>
-      <c r="J23" s="53"/>
-      <c r="K23" s="12">
-        <f>K20</f>
-        <v>946.68000000000006</v>
+      <c r="A23" s="53" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="54"/>
+      <c r="C23" s="54"/>
+      <c r="D23" s="54"/>
+      <c r="E23" s="54"/>
+      <c r="F23" s="54"/>
+      <c r="G23" s="54"/>
+      <c r="H23" s="54"/>
+      <c r="I23" s="54"/>
+      <c r="J23" s="55"/>
+      <c r="K23" s="13">
+        <f>J19</f>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A24" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="52"/>
-      <c r="C24" s="52"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="52"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="52"/>
-      <c r="J24" s="53"/>
-      <c r="K24" s="13">
-        <f>J20</f>
-        <v>266.82</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A25" s="51" t="s">
+      <c r="A24" s="53" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="52"/>
-      <c r="C25" s="52"/>
-      <c r="D25" s="52"/>
-      <c r="E25" s="52"/>
-      <c r="F25" s="52"/>
-      <c r="G25" s="52"/>
-      <c r="H25" s="52"/>
-      <c r="I25" s="52"/>
-      <c r="J25" s="53"/>
-      <c r="K25" s="12">
-        <f>K23-K24</f>
-        <v>679.86000000000013</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="48" t="s">
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="54"/>
+      <c r="I24" s="54"/>
+      <c r="J24" s="55"/>
+      <c r="K24" s="12">
+        <f>K22-K23</f>
+        <v>496.21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="49"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="50"/>
-      <c r="I27" s="50"/>
-      <c r="J27" s="50"/>
-      <c r="K27" s="50"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="49"/>
+      <c r="J26" s="49"/>
+      <c r="K26" s="49"/>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="J28" s="44"/>
+      <c r="K28" s="43">
+        <f>SUMIF($D$5:$D$17,J28,$I$5:$I$17)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="J29" s="44"/>
+      <c r="J29" s="44" t="s">
+        <v>14</v>
+      </c>
       <c r="K29" s="43">
-        <f>SUMIF($D$5:$D$18,J29,$I$5:$I$18)</f>
+        <f>SUMIF($D$5:$D$17,J29,$I$5:$I$17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="J30" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="43">
-        <f>SUMIF($D$5:$D$18,J30,$I$5:$I$18)</f>
-        <v>187.06</v>
+      <c r="J30" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="K30" s="47">
+        <f>SUMIF($D$5:$D$17,J30,$I$5:$I$17)</f>
+        <v>496.21</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="J31" s="46" t="s">
-        <v>15</v>
-      </c>
-      <c r="K31" s="47">
-        <f>SUMIF($D$5:$D$18,J31,$I$5:$I$18)</f>
-        <v>492.8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="J32"/>
-      <c r="K32" s="45">
-        <f>SUM(K29:K31)</f>
-        <v>679.86</v>
+      <c r="J31"/>
+      <c r="K31" s="45">
+        <f>SUM(K28:K30)</f>
+        <v>496.21</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I18" xr:uid="{44F60687-3931-4551-ABBC-9C01622620C5}">
+  <autoFilter ref="A4:I17" xr:uid="{44F60687-3931-4551-ABBC-9C01622620C5}">
     <filterColumn colId="3">
       <filters>
         <filter val="Amazon"/>
@@ -3082,15 +3124,22 @@
         <filter val="Lowes"/>
       </filters>
     </filterColumn>
+    <filterColumn colId="6">
+      <filters>
+        <filter val="1"/>
+        <filter val="2"/>
+        <filter val="6"/>
+      </filters>
+    </filterColumn>
   </autoFilter>
   <mergeCells count="7">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A26:K26"/>
+    <mergeCell ref="A22:J22"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A24:J24"/>
-    <mergeCell ref="A25:J25"/>
-    <mergeCell ref="A22:K22"/>
+    <mergeCell ref="A21:K21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3106,38 +3155,38 @@
     <col min="3" max="3" width="18" style="28" customWidth="1"/>
     <col min="4" max="6" width="14" style="28" customWidth="1"/>
     <col min="7" max="7" width="13" style="31" customWidth="1"/>
-    <col min="8" max="9" width="15" style="31" customWidth="1"/>
-    <col min="10" max="10" width="17" style="31" customWidth="1"/>
-    <col min="12" max="12" width="28.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.90625" style="31" customWidth="1"/>
+    <col min="10" max="10" width="16.90625" style="31" customWidth="1"/>
+    <col min="12" max="12" width="28.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="19.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
-      <c r="I1" s="50"/>
-      <c r="J1" s="50"/>
+      <c r="A1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="57"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="4" spans="1:14" ht="26" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
@@ -3174,14 +3223,14 @@
         <v>9</v>
       </c>
       <c r="B5" s="59"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="50"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="49"/>
+      <c r="I5" s="49"/>
+      <c r="J5" s="49"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
@@ -3227,14 +3276,14 @@
         <v>12</v>
       </c>
       <c r="B7" s="59"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
@@ -3317,14 +3366,14 @@
         <v>16</v>
       </c>
       <c r="B10" s="59"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="50"/>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="50"/>
-      <c r="J10" s="50"/>
+      <c r="C10" s="49"/>
+      <c r="D10" s="49"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="49"/>
+      <c r="G10" s="49"/>
+      <c r="H10" s="49"/>
+      <c r="I10" s="49"/>
+      <c r="J10" s="49"/>
       <c r="M10" s="27"/>
       <c r="N10" s="27"/>
     </row>
@@ -3447,14 +3496,14 @@
         <v>19</v>
       </c>
       <c r="B14" s="59"/>
-      <c r="C14" s="50"/>
-      <c r="D14" s="50"/>
-      <c r="E14" s="50"/>
-      <c r="F14" s="50"/>
-      <c r="G14" s="50"/>
-      <c r="H14" s="50"/>
-      <c r="I14" s="50"/>
-      <c r="J14" s="50"/>
+      <c r="C14" s="49"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
+      <c r="H14" s="49"/>
+      <c r="I14" s="49"/>
+      <c r="J14" s="49"/>
       <c r="M14" s="27"/>
       <c r="N14" s="27"/>
     </row>
@@ -3501,14 +3550,14 @@
         <v>21</v>
       </c>
       <c r="B16" s="59"/>
-      <c r="C16" s="50"/>
-      <c r="D16" s="50"/>
-      <c r="E16" s="50"/>
-      <c r="F16" s="50"/>
-      <c r="G16" s="50"/>
-      <c r="H16" s="50"/>
-      <c r="I16" s="50"/>
-      <c r="J16" s="50"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="4" t="s">
@@ -3553,14 +3602,14 @@
         <v>24</v>
       </c>
       <c r="B18" s="59"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="50"/>
-      <c r="G18" s="50"/>
-      <c r="H18" s="50"/>
-      <c r="I18" s="50"/>
-      <c r="J18" s="50"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="49"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="49"/>
+      <c r="I18" s="49"/>
+      <c r="J18" s="49"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
@@ -3605,14 +3654,14 @@
         <v>27</v>
       </c>
       <c r="B20" s="59"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="50"/>
-      <c r="J20" s="50"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="49"/>
+      <c r="E20" s="49"/>
+      <c r="F20" s="49"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="49"/>
+      <c r="I20" s="49"/>
+      <c r="J20" s="49"/>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="4" t="s">
@@ -3726,7 +3775,7 @@
       <c r="M23" s="27"/>
       <c r="N23" s="27"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" ht="26" x14ac:dyDescent="0.35">
       <c r="A24" s="4" t="s">
         <v>32</v>
       </c>
@@ -3806,10 +3855,10 @@
         <v>34</v>
       </c>
       <c r="B26" s="61"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
+      <c r="C26" s="49"/>
+      <c r="D26" s="49"/>
+      <c r="E26" s="49"/>
+      <c r="F26" s="49"/>
       <c r="G26" s="10" t="s">
         <v>35</v>
       </c>
@@ -3827,29 +3876,29 @@
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A28" s="54" t="s">
+      <c r="A28" s="56" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="55"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="50"/>
-      <c r="I28" s="50"/>
-      <c r="J28" s="50"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+      <c r="F28" s="49"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="49"/>
+      <c r="I28" s="49"/>
+      <c r="J28" s="49"/>
     </row>
     <row r="29" spans="1:14" ht="15.5" x14ac:dyDescent="0.35">
       <c r="A29" s="62" t="s">
         <v>37</v>
       </c>
       <c r="B29" s="63"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+      <c r="F29" s="49"/>
+      <c r="G29" s="49"/>
       <c r="H29" s="12">
         <f>H26</f>
         <v>1038.98</v>
@@ -3862,11 +3911,11 @@
         <v>38</v>
       </c>
       <c r="B30" s="63"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+      <c r="F30" s="49"/>
+      <c r="G30" s="49"/>
       <c r="H30" s="13">
         <f>I26</f>
         <v>266.82</v>
@@ -3879,11 +3928,11 @@
         <v>39</v>
       </c>
       <c r="B31" s="63"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
       <c r="H31" s="12">
         <f>H26-I26</f>
         <v>772.16000000000008</v>
@@ -3892,18 +3941,18 @@
       <c r="J31" s="30"/>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A33" s="48" t="s">
+      <c r="A33" s="51" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="50"/>
-      <c r="I33" s="50"/>
-      <c r="J33" s="50"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="49"/>
+      <c r="D33" s="49"/>
+      <c r="E33" s="49"/>
+      <c r="F33" s="49"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="49"/>
+      <c r="I33" s="49"/>
+      <c r="J33" s="49"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:J26" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -3933,9 +3982,9 @@
   <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="1" max="1" width="37.90625" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3943,17 +3992,17 @@
       <c r="A1" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-    </row>
-    <row r="2" spans="1:4" ht="20" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="57" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+    </row>
+    <row r="2" spans="1:4" ht="20.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
@@ -3973,9 +4022,9 @@
       <c r="A4" s="65" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
     </row>
     <row r="5" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="4" t="s">
@@ -4021,9 +4070,9 @@
       <c r="A8" s="65" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
     </row>
     <row r="9" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
@@ -4069,9 +4118,9 @@
       <c r="A12" s="65" t="s">
         <v>61</v>
       </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
-      <c r="D12" s="50"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
     </row>
     <row r="13" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
@@ -4137,9 +4186,9 @@
       <c r="A18" s="65" t="s">
         <v>70</v>
       </c>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="50"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="49"/>
     </row>
     <row r="19" spans="1:4" ht="22" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="4" t="s">
@@ -4200,4 +4249,222 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70748832-8F7B-4935-AB83-BF319E748BB1}">
+  <dimension ref="B2:K12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="3" width="8.7265625" style="28"/>
+    <col min="5" max="5" width="8.7265625" style="71"/>
+    <col min="7" max="7" width="8.7265625" style="69"/>
+    <col min="11" max="11" width="8.7265625" style="69"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:11" s="28" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="B2" s="28" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="E2" s="66" t="s">
+        <v>107</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="G2" s="67" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>111</v>
+      </c>
+      <c r="K2" s="68"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="28">
+        <v>4</v>
+      </c>
+      <c r="C3" s="28">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="69">
+        <v>37.479999999999997</v>
+      </c>
+      <c r="F3">
+        <f>B3*C3</f>
+        <v>32</v>
+      </c>
+      <c r="G3" s="69">
+        <f>E3/F3</f>
+        <v>1.1712499999999999</v>
+      </c>
+      <c r="H3">
+        <f>ROUNDUP(($C$9/F3),0)</f>
+        <v>6</v>
+      </c>
+      <c r="I3" s="70">
+        <f>H3*E3</f>
+        <v>224.88</v>
+      </c>
+      <c r="K3" s="69">
+        <v>216.97406249999997</v>
+      </c>
+    </row>
+    <row r="4" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B4" s="28">
+        <v>2</v>
+      </c>
+      <c r="C4" s="28">
+        <v>4</v>
+      </c>
+      <c r="D4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="69">
+        <v>14.98</v>
+      </c>
+      <c r="F4">
+        <f>B4*C4</f>
+        <v>8</v>
+      </c>
+      <c r="G4" s="69">
+        <f>E4/F4</f>
+        <v>1.8725000000000001</v>
+      </c>
+      <c r="H4">
+        <f t="shared" ref="H4:H7" si="0">ROUNDUP(($C$9/F4),0)</f>
+        <v>23</v>
+      </c>
+      <c r="I4" s="70">
+        <f t="shared" ref="I4:I7" si="1">H4*E4</f>
+        <v>344.54</v>
+      </c>
+      <c r="K4" s="69">
+        <v>346.88062500000001</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B5" s="28">
+        <v>2</v>
+      </c>
+      <c r="C5" s="28">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="69">
+        <v>7.98</v>
+      </c>
+      <c r="F5">
+        <f>B5*C5</f>
+        <v>4</v>
+      </c>
+      <c r="G5" s="69">
+        <f>E5/F5</f>
+        <v>1.9950000000000001</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I5" s="70">
+        <f t="shared" si="1"/>
+        <v>367.08000000000004</v>
+      </c>
+      <c r="K5" s="69">
+        <v>369.57375000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B6" s="28">
+        <v>2</v>
+      </c>
+      <c r="C6" s="28">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="69">
+        <v>22.78</v>
+      </c>
+      <c r="F6">
+        <f>B6*C6</f>
+        <v>8</v>
+      </c>
+      <c r="G6" s="69">
+        <f>E6/F6</f>
+        <v>2.8475000000000001</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+      <c r="I6" s="70">
+        <f t="shared" si="1"/>
+        <v>523.94000000000005</v>
+      </c>
+      <c r="K6" s="69">
+        <v>527.49937499999999</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B7" s="28">
+        <v>2</v>
+      </c>
+      <c r="C7" s="28">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>114</v>
+      </c>
+      <c r="E7" s="69">
+        <v>12.18</v>
+      </c>
+      <c r="F7">
+        <f>B7*C7</f>
+        <v>4</v>
+      </c>
+      <c r="G7" s="69">
+        <f>E7/F7</f>
+        <v>3.0449999999999999</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>46</v>
+      </c>
+      <c r="I7" s="70">
+        <f t="shared" si="1"/>
+        <v>560.28</v>
+      </c>
+      <c r="K7" s="69">
+        <v>564.08624999999995</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B9" s="28" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="28">
+        <f>'Wall Calculations'!B7</f>
+        <v>180.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="G12"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="B2:I7" xr:uid="{9774A96C-1F9D-4DDD-9028-566BA7FEE82B}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>